--- a/diseases/d240/1975-1979.xlsx
+++ b/diseases/d240/1975-1979.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN2" t="b">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN4" t="b">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">

--- a/diseases/d240/1975-1979.xlsx
+++ b/diseases/d240/1975-1979.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN2" t="b">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN4" t="b">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
